--- a/chat_shops.xlsx
+++ b/chat_shops.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/512a546b848d6679/سطح المكتب/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_2C44BDEC2040C98AC652E4A0FCF3E5041998AE35" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5758ABB6-E90B-4D1C-901E-12739151E4AA}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="11_2C44BDEC2040C98AC652E4A0FCF3E5041998AE35" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A853D5F-FC2C-4290-B8CF-36A650BFAD67}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
   <si>
     <t>shop_name</t>
   </si>
@@ -48,9 +48,6 @@
     <t>ملابس</t>
   </si>
   <si>
-    <t>البروم</t>
-  </si>
-  <si>
     <t>نساء</t>
   </si>
   <si>
@@ -82,6 +79,12 @@
   </si>
   <si>
     <t>الدور الأرضي</t>
+  </si>
+  <si>
+    <t>منزل</t>
+  </si>
+  <si>
+    <t>البدوم</t>
   </si>
 </sst>
 </file>
@@ -134,6 +137,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -433,7 +440,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -441,13 +448,13 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -455,13 +462,13 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -469,69 +476,69 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
         <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
         <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/chat_shops.xlsx
+++ b/chat_shops.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/512a546b848d6679/سطح المكتب/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="11_2C44BDEC2040C98AC652E4A0FCF3E5041998AE35" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A853D5F-FC2C-4290-B8CF-36A650BFAD67}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_2C44BDEC2040C98AC652E4A0FCF3E5041998AE35" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C225311C-0E6C-4732-8EE7-C2493EC6F0B6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
   <si>
     <t>shop_name</t>
   </si>
@@ -85,6 +85,12 @@
   </si>
   <si>
     <t>البدوم</t>
+  </si>
+  <si>
+    <t>السينما</t>
+  </si>
+  <si>
+    <t>سينما</t>
   </si>
 </sst>
 </file>
@@ -406,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.796875" customWidth="1"/>
@@ -541,6 +547,20 @@
         <v>17</v>
       </c>
     </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/chat_shops.xlsx
+++ b/chat_shops.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/512a546b848d6679/سطح المكتب/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="11_2C44BDEC2040C98AC652E4A0FCF3E5041998AE35" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C225311C-0E6C-4732-8EE7-C2493EC6F0B6}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="11_2C44BDEC2040C98AC652E4A0FCF3E5041998AE35" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48541788-BA6B-407C-A023-661A6ED1A121}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2856" yWindow="2856" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
   <si>
     <t>shop_name</t>
   </si>
@@ -91,6 +91,21 @@
   </si>
   <si>
     <t>سينما</t>
+  </si>
+  <si>
+    <t>أطفال علماء</t>
+  </si>
+  <si>
+    <t>ترفيه والعاب</t>
+  </si>
+  <si>
+    <t>حضانة سارة</t>
+  </si>
+  <si>
+    <t>حضانة</t>
+  </si>
+  <si>
+    <t>الدور الأول</t>
   </si>
 </sst>
 </file>
@@ -412,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.796875" customWidth="1"/>
@@ -561,6 +576,34 @@
         <v>12</v>
       </c>
     </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/chat_shops.xlsx
+++ b/chat_shops.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/512a546b848d6679/سطح المكتب/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rosea\OneDrive\سطح المكتب\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="11_2C44BDEC2040C98AC652E4A0FCF3E5041998AE35" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48541788-BA6B-407C-A023-661A6ED1A121}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE8FB04-8C1C-492B-BBB6-BCDBA1ECF24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2856" yWindow="2856" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
@@ -25,99 +25,473 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="149">
   <si>
     <t>shop_name</t>
   </si>
   <si>
-    <t>target_audience</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
     <t>location</t>
   </si>
   <si>
     <t>سنتربوينت</t>
   </si>
   <si>
-    <t>أطفال</t>
-  </si>
-  <si>
-    <t>ملابس</t>
-  </si>
-  <si>
-    <t>نساء</t>
-  </si>
-  <si>
-    <t>رجال</t>
-  </si>
-  <si>
-    <t>الكل</t>
-  </si>
-  <si>
     <t>صب واي</t>
   </si>
   <si>
-    <t>مطاعم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الدور الثاني </t>
-  </si>
-  <si>
     <t>كودو</t>
   </si>
   <si>
     <t>ماما بنز</t>
   </si>
   <si>
-    <t>مقاهي</t>
-  </si>
-  <si>
-    <t>بول</t>
-  </si>
-  <si>
-    <t>الدور الأرضي</t>
-  </si>
-  <si>
-    <t>منزل</t>
-  </si>
-  <si>
-    <t>البدوم</t>
-  </si>
-  <si>
     <t>السينما</t>
   </si>
   <si>
-    <t>سينما</t>
-  </si>
-  <si>
-    <t>أطفال علماء</t>
-  </si>
-  <si>
-    <t>ترفيه والعاب</t>
-  </si>
-  <si>
-    <t>حضانة سارة</t>
-  </si>
-  <si>
-    <t>حضانة</t>
-  </si>
-  <si>
-    <t>الدور الأول</t>
+    <t>اساور رنيم</t>
+  </si>
+  <si>
+    <t>اديداس</t>
+  </si>
+  <si>
+    <t>موج فون</t>
+  </si>
+  <si>
+    <t>نعومي</t>
+  </si>
+  <si>
+    <t>كيكو</t>
+  </si>
+  <si>
+    <t>شو اكسبرس</t>
+  </si>
+  <si>
+    <t>البدروم</t>
+  </si>
+  <si>
+    <t>الرفاعي</t>
+  </si>
+  <si>
+    <t>مكينة حلوى غزل البنات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بول </t>
+  </si>
+  <si>
+    <t>هوم بوكس</t>
+  </si>
+  <si>
+    <t>هوم سنتر</t>
+  </si>
+  <si>
+    <t>النهدي</t>
+  </si>
+  <si>
+    <t>بلومنج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">درومز </t>
+  </si>
+  <si>
+    <t>لفته</t>
+  </si>
+  <si>
+    <t>العربية للعود</t>
+  </si>
+  <si>
+    <t>عود اند كو</t>
+  </si>
+  <si>
+    <t>وايتس</t>
+  </si>
+  <si>
+    <t>ايف روشيه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تيلا هوم </t>
+  </si>
+  <si>
+    <t>ماكس</t>
+  </si>
+  <si>
+    <t>الرصاصي</t>
+  </si>
+  <si>
+    <t>جيوردانو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اي لاهوي </t>
+  </si>
+  <si>
+    <t>بارنز</t>
+  </si>
+  <si>
+    <t>واحة الجلابية</t>
+  </si>
+  <si>
+    <t>دخون</t>
+  </si>
+  <si>
+    <t>ميني سو</t>
+  </si>
+  <si>
+    <t>بريق الفضة</t>
+  </si>
+  <si>
+    <t>لميس</t>
+  </si>
+  <si>
+    <t>رمز الفضة</t>
+  </si>
+  <si>
+    <t>البارو</t>
+  </si>
+  <si>
+    <t>اوفاز للفضة</t>
+  </si>
+  <si>
+    <t>سكتشرز</t>
+  </si>
+  <si>
+    <t>فايندرا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اطفال واكثر </t>
+  </si>
+  <si>
+    <t>ان هاوس</t>
+  </si>
+  <si>
+    <t>موموسو</t>
+  </si>
+  <si>
+    <t>نخبة العود</t>
+  </si>
+  <si>
+    <t>اصول الحلا</t>
+  </si>
+  <si>
+    <t>هابي بوث</t>
+  </si>
+  <si>
+    <t>درعه</t>
+  </si>
+  <si>
+    <t>جاسمن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عطر حصري </t>
+  </si>
+  <si>
+    <t>ستاربكس</t>
+  </si>
+  <si>
+    <t>ار اند بي</t>
+  </si>
+  <si>
+    <t>ماتش</t>
+  </si>
+  <si>
+    <t>كارفور</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ابراق </t>
+  </si>
+  <si>
+    <t>الماجد للعود</t>
+  </si>
+  <si>
+    <t>عبدالصمد القرشي</t>
+  </si>
+  <si>
+    <t>بلو ايج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">باث اند بودي وركس </t>
+  </si>
+  <si>
+    <t>كول هان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كراميل باث اند بودي </t>
+  </si>
+  <si>
+    <t>بالمان</t>
+  </si>
+  <si>
+    <t>ميلانو</t>
+  </si>
+  <si>
+    <t>اتش اند ام</t>
+  </si>
+  <si>
+    <t>استيري</t>
+  </si>
+  <si>
+    <t>يولا</t>
+  </si>
+  <si>
+    <t>بييركاردان</t>
+  </si>
+  <si>
+    <t>كارديال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اجمل </t>
+  </si>
+  <si>
+    <t>ماركس و سبنسر</t>
+  </si>
+  <si>
+    <t>داماس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مهيار </t>
+  </si>
+  <si>
+    <t>ايوا</t>
+  </si>
+  <si>
+    <t>بولو</t>
+  </si>
+  <si>
+    <t>سيفورا</t>
+  </si>
+  <si>
+    <t>تيم هورتنز</t>
+  </si>
+  <si>
+    <t>لابوتيه</t>
+  </si>
+  <si>
+    <t>نكست</t>
+  </si>
+  <si>
+    <t>مسك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خفيف </t>
+  </si>
+  <si>
+    <t>زين</t>
+  </si>
+  <si>
+    <t xml:space="preserve">غناتي </t>
+  </si>
+  <si>
+    <t>لولو جلاس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دخون الاماراتية </t>
+  </si>
+  <si>
+    <t>اوسما</t>
+  </si>
+  <si>
+    <t>ريف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لي ڤان </t>
+  </si>
+  <si>
+    <t>بلانكو</t>
+  </si>
+  <si>
+    <t>تولي جور</t>
+  </si>
+  <si>
+    <t>الحميضي</t>
+  </si>
+  <si>
+    <t>استريا</t>
+  </si>
+  <si>
+    <t>قصة</t>
+  </si>
+  <si>
+    <t>رسيس</t>
+  </si>
+  <si>
+    <t>بلوم</t>
+  </si>
+  <si>
+    <t>لذة وحلا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ماكدونالدز </t>
+  </si>
+  <si>
+    <t>شاورما ستور</t>
+  </si>
+  <si>
+    <t xml:space="preserve">باسكن روبنز </t>
+  </si>
+  <si>
+    <t>لافينا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دومينوز </t>
+  </si>
+  <si>
+    <t>اطفال علماء</t>
+  </si>
+  <si>
+    <t>بابا جونز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هارديز </t>
+  </si>
+  <si>
+    <t>بيتزا عالحطب لينيو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كانتون </t>
+  </si>
+  <si>
+    <t>فلافينا</t>
+  </si>
+  <si>
+    <t>روما واي</t>
+  </si>
+  <si>
+    <t>صرح</t>
+  </si>
+  <si>
+    <t>موفنبيك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هوفي </t>
+  </si>
+  <si>
+    <t>سبأ</t>
+  </si>
+  <si>
+    <t>كومبير</t>
+  </si>
+  <si>
+    <t>ابل بيز</t>
+  </si>
+  <si>
+    <t>ماريوت</t>
+  </si>
+  <si>
+    <t>الدور الاول</t>
+  </si>
+  <si>
+    <t>الدور الارضي</t>
+  </si>
+  <si>
+    <t>الدور الثاني</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سباركيز  </t>
+  </si>
+  <si>
+    <t>بلو ستار</t>
+  </si>
+  <si>
+    <t>ميدي</t>
+  </si>
+  <si>
+    <t>برايفت</t>
+  </si>
+  <si>
+    <t>تمارا</t>
+  </si>
+  <si>
+    <t>الجوهرة</t>
+  </si>
+  <si>
+    <t>لافال</t>
+  </si>
+  <si>
+    <t>تومي هيلفيغر</t>
+  </si>
+  <si>
+    <t>كالفين كلاين</t>
+  </si>
+  <si>
+    <t>كيو اند ايه</t>
+  </si>
+  <si>
+    <t>ذا بودي شوب</t>
+  </si>
+  <si>
+    <t>مكرونة روما</t>
+  </si>
+  <si>
+    <t>كنتاكي</t>
+  </si>
+  <si>
+    <t>فيمي ناين</t>
+  </si>
+  <si>
+    <t>غارام ماسالا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">برجر كنج </t>
+  </si>
+  <si>
+    <t>تكساس تشيكن</t>
+  </si>
+  <si>
+    <t>تشيل كب</t>
+  </si>
+  <si>
+    <t>بيرفيوم الكسير</t>
+  </si>
+  <si>
+    <t>سيزون لايتس</t>
+  </si>
+  <si>
+    <t>ميتل كوفي</t>
+  </si>
+  <si>
+    <t>كيدز باربر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الجربوع  </t>
+  </si>
+  <si>
+    <t>اوبشن بي</t>
+  </si>
+  <si>
+    <t>فتنس فروت</t>
+  </si>
+  <si>
+    <t>منصور رشوان</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> العاب سيارات متجولة</t>
+  </si>
+  <si>
+    <t>ليو جو</t>
+  </si>
+  <si>
+    <t>العاب سيارات متجولة</t>
+  </si>
+  <si>
+    <t>صراف</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="178"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -138,14 +512,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
+    <cellStyle name="عادي 2" xfId="1" xr:uid="{ED69908A-DDDD-41DD-AA91-088AFA44186F}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -158,10 +539,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -427,181 +804,1163 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:B144"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.796875" customWidth="1"/>
-    <col min="2" max="2" width="15.09765625" customWidth="1"/>
-    <col min="3" max="3" width="14.19921875" customWidth="1"/>
-    <col min="4" max="4" width="11.69921875" customWidth="1"/>
+    <col min="2" max="2" width="11.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B124" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B130" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B136" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" t="s">
-        <v>26</v>
+      <c r="B141" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
